--- a/erp-server/erp-server-scm/src/main/resources/excel/sysUserExport.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/sysUserExport.xlsx
@@ -88,13 +88,13 @@
     <t>{.isBindWechatStr}</t>
   </si>
   <si>
-    <t>{.lastLoginTime}</t>
+    <t>{.lastLoginTimeStr}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
   </si>
   <si>
-    <t>{.createTime}</t>
+    <t>{.createTimeStr}</t>
   </si>
 </sst>
 </file>

--- a/erp-server/erp-server-scm/src/main/resources/excel/sysUserExport.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/sysUserExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27525" windowHeight="4440"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,16 +73,16 @@
     <t>{.email}</t>
   </si>
   <si>
+    <t>{.isSuperStr}</t>
+  </si>
+  <si>
+    <t>{.supplierName}</t>
+  </si>
+  <si>
+    <t>{.purchaseUserName}</t>
+  </si>
+  <si>
     <t>{.userStateStr}</t>
-  </si>
-  <si>
-    <t>{.supplierName}</t>
-  </si>
-  <si>
-    <t>{.purchaseUserName}</t>
-  </si>
-  <si>
-    <t>{.disabledStr}</t>
   </si>
   <si>
     <t>{.isBindWechatStr}</t>
